--- a/Temp2.xlsx
+++ b/Temp2.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SFDCConfigTable" displayName="SFDCConfigTable" ref="A2:F32" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SFDCConfigTable" displayName="SFDCConfigTable" ref="A2:G32" headerRowCount="1">
   <autoFilter ref="A2:F32"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Cloud"/>
@@ -272,7 +272,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MaximoConfigTable" displayName="MaximoConfigTable" ref="A2:F8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MaximoConfigTable" displayName="MaximoConfigTable" ref="A2:G8" headerRowCount="1">
   <autoFilter ref="A2:F8"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Module"/>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:D16" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E16" headerRowCount="1">
   <autoFilter ref="A2:D16"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Testing Area"/>
@@ -313,7 +313,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="AutomationLifecycleRatesTable" displayName="AutomationLifecycleRatesTable" ref="A2:K22" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="AutomationLifecycleRatesTable" displayName="AutomationLifecycleRatesTable" ref="A2:L22" headerRowCount="1">
   <autoFilter ref="A2:K22"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Tool"/>
@@ -333,7 +333,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="PerformanceLifecycleRatesTable" displayName="PerformanceLifecycleRatesTable" ref="A2:L32" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="PerformanceLifecycleRatesTable" displayName="PerformanceLifecycleRatesTable" ref="A2:M32" headerRowCount="1">
   <autoFilter ref="A2:L32"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Performance Type"/>
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="IndustryAcceleratorsTable" displayName="IndustryAcceleratorsTable" ref="A2:F7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="IndustryAcceleratorsTable" displayName="IndustryAcceleratorsTable" ref="A2:G7" headerRowCount="1">
   <autoFilter ref="A2:F7"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Accelerator"/>
@@ -514,7 +514,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SAPImplementationTypeTable" displayName="SAPImplementationTypeTable" ref="A2:E7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SAPImplementationTypeTable" displayName="SAPImplementationTypeTable" ref="A2:F7" headerRowCount="1">
   <autoFilter ref="A2:E7"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Implementation Type"/>
@@ -528,7 +528,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SAPDeploymentReuseTable" displayName="SAPDeploymentReuseTable" ref="A2:F6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SAPDeploymentReuseTable" displayName="SAPDeploymentReuseTable" ref="A2:G6" headerRowCount="1">
   <autoFilter ref="A2:F6"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Wave"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1111,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,6 +1152,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SFDCConfigKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1177,6 +1183,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Sales Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1203,6 +1214,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Sales Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1229,6 +1245,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Sales Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1255,6 +1276,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Sales Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1281,6 +1307,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Sales Cloud|Validation Rules</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1307,6 +1338,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Service Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1333,6 +1369,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Service Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1359,6 +1400,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Service Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1385,6 +1431,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Service Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1411,6 +1462,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Service Cloud|Validation Rules</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1437,6 +1493,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Experience Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1463,6 +1524,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Experience Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1489,6 +1555,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Experience Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1515,6 +1586,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Experience Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1541,6 +1617,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Experience Cloud|Validation Rules</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1567,6 +1648,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1593,6 +1679,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1619,6 +1710,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1645,6 +1741,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1671,6 +1772,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Cloud|Validation Rules</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1697,6 +1803,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Revenue Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1723,6 +1834,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Revenue Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1749,6 +1865,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Revenue Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1775,6 +1896,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Revenue Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1801,6 +1927,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Revenue Cloud|Validation Rules</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1827,6 +1958,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Data Cloud|Custom Objects</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1853,6 +1989,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Data Cloud|Flows</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1879,6 +2020,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Data Cloud|Apex Classes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1905,6 +2051,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Data Cloud|LWC Components</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1929,6 +2080,11 @@
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Data Cloud|Validation Rules</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1958,6 +2114,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1998,6 +2155,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>MaximoConfigKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2024,6 +2186,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Work Order Management|Work Order Planning</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2050,6 +2217,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Asset Management|Asset Lifecycle</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2076,6 +2248,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance|Preventive Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2102,6 +2279,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Inventory Management|Inventory Replenishment</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2128,6 +2310,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Procurement|Procurement Request Flow</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2152,6 +2339,11 @@
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Service Requests|Service Request Intake</t>
         </is>
       </c>
     </row>
@@ -2307,13 +2499,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2344,6 +2537,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ApplicabilityKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2364,6 +2562,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Manual|Functional</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2384,6 +2587,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Manual|API</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2404,6 +2612,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Manual|Integration</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2424,6 +2637,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Manual|SIT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2444,6 +2662,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Manual|E2E</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2464,6 +2687,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Manual|Manual Regression</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2484,6 +2712,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Automation|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2504,6 +2737,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Automation|Design / Scripting</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2524,6 +2762,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Automation|Test Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2544,6 +2787,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Automation|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2564,6 +2812,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Automation|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2584,6 +2837,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Performance|Load</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2604,6 +2862,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Performance|Stress</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2622,6 +2885,11 @@
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Performance|Endurance</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -2656,6 +2924,7 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2721,6 +2990,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>AutomationRateKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2764,6 +3038,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Selenium|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2807,6 +3086,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Selenium|Design / Scripting</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2850,6 +3134,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Selenium|Test Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2893,6 +3182,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Selenium|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2936,6 +3230,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Selenium|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2979,6 +3278,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Playwright|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3022,6 +3326,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Playwright|Design / Scripting</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -3065,6 +3374,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Playwright|Test Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3108,6 +3422,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Playwright|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3151,6 +3470,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Playwright|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3194,6 +3518,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Tosca|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3237,6 +3566,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Tosca|Design / Scripting</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3280,6 +3614,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Tosca|Test Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3323,6 +3662,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Tosca|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3366,6 +3710,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Tosca|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3409,6 +3758,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Worksoft|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3452,6 +3806,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Worksoft|Design / Scripting</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3495,6 +3854,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Worksoft|Test Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3538,6 +3902,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Worksoft|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3579,6 +3948,11 @@
       <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Worksoft|Execution</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3614,6 +3988,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3684,6 +4059,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>PerformanceRateKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3732,6 +4112,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Load|LoadRunner|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3780,6 +4165,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Load|LoadRunner|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3828,6 +4218,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Load|LoadRunner|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3876,6 +4271,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Load|LoadRunner|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3924,6 +4324,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Load|LoadRunner|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -3972,6 +4377,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Load|NeoLoad|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4020,6 +4430,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Load|NeoLoad|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4068,6 +4483,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Load|NeoLoad|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4116,6 +4536,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Load|NeoLoad|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4164,6 +4589,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Load|NeoLoad|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4212,6 +4642,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Stress|LoadRunner|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -4260,6 +4695,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Stress|LoadRunner|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4308,6 +4748,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Stress|LoadRunner|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -4356,6 +4801,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Stress|LoadRunner|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4404,6 +4854,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Stress|LoadRunner|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4452,6 +4907,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Stress|NeoLoad|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4500,6 +4960,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Stress|NeoLoad|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4548,6 +5013,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Stress|NeoLoad|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4596,6 +5066,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Stress|NeoLoad|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4644,6 +5119,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Stress|NeoLoad|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -4692,6 +5172,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|LoadRunner|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4740,6 +5225,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|LoadRunner|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -4788,6 +5278,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|LoadRunner|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -4836,6 +5331,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|LoadRunner|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4884,6 +5384,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|LoadRunner|Execution</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4932,6 +5437,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|NeoLoad|Script Design / Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4980,6 +5490,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|NeoLoad|Data Prep</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -5028,6 +5543,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|NeoLoad|Dry Run</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -5076,6 +5596,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|NeoLoad|Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -5122,6 +5647,11 @@
       <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Endurance|NeoLoad|Execution</t>
         </is>
       </c>
     </row>
@@ -7800,7 +8330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7809,6 +8339,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7849,6 +8380,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>AcceleratorKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -7875,6 +8411,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Standard|All</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7901,6 +8442,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>SAP IS-U|Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7927,6 +8473,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>IS-Retail|Retail</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7953,6 +8504,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>IS-Oil&amp;Gas|Oil &amp; Gas</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7977,6 +8533,11 @@
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>GxP/Validation|Life Sciences</t>
         </is>
       </c>
     </row>
@@ -7997,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8005,6 +8566,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8040,6 +8602,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ImplementationKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -8063,6 +8630,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Greenfield|Data Load Validation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -8086,6 +8658,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Brownfield|Custom Code Objects for Regression</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -8109,6 +8686,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Brownfield|Data Conversion Validation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -8132,6 +8714,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Bluefield|Custom Code Objects for Regression</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -8153,6 +8740,11 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bluefield|Data Reconciliation Objects</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -8182,6 +8774,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8222,6 +8815,11 @@
           <t>Active (Y/N)</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>DeploymentReuseKey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -8248,6 +8846,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Pilot Only|Pilot</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -8274,6 +8877,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Pilot + Rollout|Canada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -8300,6 +8908,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Pilot + Rollout|Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -8324,6 +8937,11 @@
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Pilot + Rollout|UK</t>
         </is>
       </c>
     </row>

--- a/Temp2.xlsx
+++ b/Temp2.xlsx
@@ -258,14 +258,15 @@
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SFDCConfigTable" displayName="SFDCConfigTable" ref="A2:G32" headerRowCount="1">
-  <autoFilter ref="A2:F32"/>
-  <tableColumns count="6">
+  <autoFilter ref="A2:G32"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="Cloud"/>
     <tableColumn id="2" name="Scope Object Type"/>
     <tableColumn id="3" name="Simple Multiplier"/>
     <tableColumn id="4" name="Medium Multiplier"/>
     <tableColumn id="5" name="Complex Multiplier"/>
     <tableColumn id="6" name="Active (Y/N)"/>
+    <tableColumn id="7" name="SFDCConfigKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -273,14 +274,15 @@
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MaximoConfigTable" displayName="MaximoConfigTable" ref="A2:G8" headerRowCount="1">
-  <autoFilter ref="A2:F8"/>
-  <tableColumns count="6">
+  <autoFilter ref="A2:G8"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="Module"/>
     <tableColumn id="2" name="Process"/>
     <tableColumn id="3" name="Simple Multiplier"/>
     <tableColumn id="4" name="Medium Multiplier"/>
     <tableColumn id="5" name="Complex Multiplier"/>
     <tableColumn id="6" name="Active (Y/N)"/>
+    <tableColumn id="7" name="MaximoConfigKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -301,12 +303,13 @@
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E16" headerRowCount="1">
-  <autoFilter ref="A2:D16"/>
-  <tableColumns count="4">
+  <autoFilter ref="A2:E16"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="Testing Area"/>
     <tableColumn id="2" name="Sub-Type"/>
     <tableColumn id="3" name="Suggested Basis %"/>
     <tableColumn id="4" name="Active (Y/N)"/>
+    <tableColumn id="5" name="ApplicabilityKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -314,8 +317,8 @@
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="AutomationLifecycleRatesTable" displayName="AutomationLifecycleRatesTable" ref="A2:L22" headerRowCount="1">
-  <autoFilter ref="A2:K22"/>
-  <tableColumns count="11">
+  <autoFilter ref="A2:L22"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Tool"/>
     <tableColumn id="2" name="Lifecycle Stage"/>
     <tableColumn id="3" name="XS"/>
@@ -327,6 +330,7 @@
     <tableColumn id="9" name="Default Reuse %"/>
     <tableColumn id="10" name="Default AI %"/>
     <tableColumn id="11" name="Active (Y/N)"/>
+    <tableColumn id="12" name="AutomationRateKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -334,8 +338,8 @@
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="PerformanceLifecycleRatesTable" displayName="PerformanceLifecycleRatesTable" ref="A2:M32" headerRowCount="1">
-  <autoFilter ref="A2:L32"/>
-  <tableColumns count="12">
+  <autoFilter ref="A2:M32"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Performance Type"/>
     <tableColumn id="2" name="Tool"/>
     <tableColumn id="3" name="Lifecycle Stage"/>
@@ -348,6 +352,7 @@
     <tableColumn id="10" name="Default Reuse %"/>
     <tableColumn id="11" name="Default AI %"/>
     <tableColumn id="12" name="Active (Y/N)"/>
+    <tableColumn id="13" name="PerformanceRateKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -500,14 +505,15 @@
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="IndustryAcceleratorsTable" displayName="IndustryAcceleratorsTable" ref="A2:G7" headerRowCount="1">
-  <autoFilter ref="A2:F7"/>
-  <tableColumns count="6">
+  <autoFilter ref="A2:G7"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="Accelerator"/>
     <tableColumn id="2" name="Sector"/>
     <tableColumn id="3" name="Process Multiplier"/>
     <tableColumn id="4" name="WRICEF Multiplier"/>
     <tableColumn id="5" name="Integration Multiplier"/>
     <tableColumn id="6" name="Active (Y/N)"/>
+    <tableColumn id="7" name="AcceleratorKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -515,13 +521,14 @@
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SAPImplementationTypeTable" displayName="SAPImplementationTypeTable" ref="A2:F7" headerRowCount="1">
-  <autoFilter ref="A2:E7"/>
-  <tableColumns count="5">
+  <autoFilter ref="A2:F7"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Implementation Type"/>
     <tableColumn id="2" name="Additional Scope Row"/>
     <tableColumn id="3" name="Scenario Multiplier"/>
     <tableColumn id="4" name="Rate Modifier"/>
     <tableColumn id="5" name="Active (Y/N)"/>
+    <tableColumn id="6" name="ImplementationKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -529,14 +536,15 @@
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SAPDeploymentReuseTable" displayName="SAPDeploymentReuseTable" ref="A2:G6" headerRowCount="1">
-  <autoFilter ref="A2:F6"/>
-  <tableColumns count="6">
+  <autoFilter ref="A2:G6"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="Wave"/>
     <tableColumn id="2" name="Country"/>
     <tableColumn id="3" name="Default Reuse %"/>
     <tableColumn id="4" name="Default Delta L4"/>
     <tableColumn id="5" name="Default Delta WRICEF"/>
     <tableColumn id="6" name="Active (Y/N)"/>
+    <tableColumn id="7" name="DeploymentReuseKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/Temp2.xlsx
+++ b/Temp2.xlsx
@@ -25,8 +25,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Rates" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade Rates" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profiles" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profile Weights" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -394,28 +395,29 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:G4" headerRowCount="1">
-  <autoFilter ref="A2:G4"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:F4" headerRowCount="1">
+  <autoFilter ref="A2:F4"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Profile"/>
-    <tableColumn id="2" name="Month Weight Pattern"/>
-    <tableColumn id="3" name="Min Team"/>
-    <tableColumn id="4" name="Peak Team"/>
-    <tableColumn id="5" name="Onshore %"/>
-    <tableColumn id="6" name="Offshore %"/>
-    <tableColumn id="7" name="Active (Y/N)"/>
+    <tableColumn id="2" name="Min Team"/>
+    <tableColumn id="3" name="Peak Team"/>
+    <tableColumn id="4" name="Onshore %"/>
+    <tableColumn id="5" name="Offshore %"/>
+    <tableColumn id="6" name="Active (Y/N)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
-  <autoFilter ref="A2:C6"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Setting"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Notes"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="StaffingProfileWeightsTable" displayName="StaffingProfileWeightsTable" ref="A2:E20" headerRowCount="1">
+  <autoFilter ref="A2:E20"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Profile"/>
+    <tableColumn id="2" name="MonthNumber"/>
+    <tableColumn id="3" name="Weight"/>
+    <tableColumn id="4" name="Active (Y/N)"/>
+    <tableColumn id="5" name="StaffingProfileWeightKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -436,7 +438,19 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
+  <autoFilter ref="A2:C6"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Setting"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
   <autoFilter ref="A2:C12"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Assumption ID"/>
@@ -462,15 +476,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SAPL1ProcessesTable" displayName="SAPL1ProcessesTable" ref="A2:F26" headerRowCount="1">
-  <autoFilter ref="A2:F26"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SAPL1ProcessesTable" displayName="SAPL1ProcessesTable" ref="A2:G74" headerRowCount="1">
+  <autoFilter ref="A2:G74"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="L1 Code"/>
     <tableColumn id="2" name="L1 Process"/>
-    <tableColumn id="3" name="Applicable Sectors"/>
+    <tableColumn id="3" name="Sector"/>
     <tableColumn id="4" name="Rule Type"/>
     <tableColumn id="5" name="Replacement Rule"/>
     <tableColumn id="6" name="Active (Y/N)"/>
+    <tableColumn id="7" name="SAPL1ProcessKey"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -504,8 +519,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="IndustryAcceleratorsTable" displayName="IndustryAcceleratorsTable" ref="A2:G7" headerRowCount="1">
-  <autoFilter ref="A2:G7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="IndustryAcceleratorsTable" displayName="IndustryAcceleratorsTable" ref="A2:G16" headerRowCount="1">
+  <autoFilter ref="A2:G16"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Accelerator"/>
     <tableColumn id="2" name="Sector"/>
@@ -1119,7 +1134,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,7 +1206,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Sales Cloud|Custom Objects</t>
         </is>
@@ -1222,7 +1237,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Sales Cloud|Flows</t>
         </is>
@@ -1253,7 +1268,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Sales Cloud|Apex Classes</t>
         </is>
@@ -1284,7 +1299,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Sales Cloud|LWC Components</t>
         </is>
@@ -1315,7 +1330,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Sales Cloud|Validation Rules</t>
         </is>
@@ -1346,7 +1361,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Service Cloud|Custom Objects</t>
         </is>
@@ -1377,7 +1392,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Service Cloud|Flows</t>
         </is>
@@ -1408,7 +1423,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Service Cloud|Apex Classes</t>
         </is>
@@ -1439,7 +1454,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Service Cloud|LWC Components</t>
         </is>
@@ -1470,7 +1485,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Service Cloud|Validation Rules</t>
         </is>
@@ -1501,7 +1516,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Experience Cloud|Custom Objects</t>
         </is>
@@ -1532,7 +1547,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Experience Cloud|Flows</t>
         </is>
@@ -1563,7 +1578,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Experience Cloud|Apex Classes</t>
         </is>
@@ -1594,7 +1609,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Experience Cloud|LWC Components</t>
         </is>
@@ -1625,7 +1640,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Experience Cloud|Validation Rules</t>
         </is>
@@ -1656,7 +1671,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Marketing Cloud|Custom Objects</t>
         </is>
@@ -1687,7 +1702,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Marketing Cloud|Flows</t>
         </is>
@@ -1718,7 +1733,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Marketing Cloud|Apex Classes</t>
         </is>
@@ -1749,7 +1764,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Marketing Cloud|LWC Components</t>
         </is>
@@ -1780,7 +1795,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Marketing Cloud|Validation Rules</t>
         </is>
@@ -1811,7 +1826,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Revenue Cloud|Custom Objects</t>
         </is>
@@ -1842,7 +1857,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Revenue Cloud|Flows</t>
         </is>
@@ -1873,7 +1888,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Revenue Cloud|Apex Classes</t>
         </is>
@@ -1904,7 +1919,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Revenue Cloud|LWC Components</t>
         </is>
@@ -1935,7 +1950,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Revenue Cloud|Validation Rules</t>
         </is>
@@ -1966,7 +1981,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Data Cloud|Custom Objects</t>
         </is>
@@ -1997,7 +2012,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Data Cloud|Flows</t>
         </is>
@@ -2028,7 +2043,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Data Cloud|Apex Classes</t>
         </is>
@@ -2059,7 +2074,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Data Cloud|LWC Components</t>
         </is>
@@ -2090,7 +2105,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Data Cloud|Validation Rules</t>
         </is>
@@ -2098,7 +2113,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2122,7 +2137,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2194,7 +2209,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Work Order Management|Work Order Planning</t>
         </is>
@@ -2225,7 +2240,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Asset Management|Asset Lifecycle</t>
         </is>
@@ -2256,7 +2271,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Preventive Maintenance|Preventive Maintenance</t>
         </is>
@@ -2287,7 +2302,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Inventory Management|Inventory Replenishment</t>
         </is>
@@ -2318,7 +2333,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Procurement|Procurement Request Flow</t>
         </is>
@@ -2349,7 +2364,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Service Requests|Service Request Intake</t>
         </is>
@@ -2357,7 +2372,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2514,7 +2529,7 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2570,7 +2585,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Manual|Functional</t>
         </is>
@@ -2595,7 +2610,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Manual|API</t>
         </is>
@@ -2620,7 +2635,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Manual|Integration</t>
         </is>
@@ -2645,7 +2660,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Manual|SIT</t>
         </is>
@@ -2670,7 +2685,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Manual|E2E</t>
         </is>
@@ -2695,7 +2710,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Manual|Manual Regression</t>
         </is>
@@ -2720,7 +2735,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Automation|Analysis</t>
         </is>
@@ -2745,7 +2760,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Automation|Design / Scripting</t>
         </is>
@@ -2770,7 +2785,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Automation|Test Data Prep</t>
         </is>
@@ -2795,7 +2810,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Automation|Dry Run</t>
         </is>
@@ -2820,7 +2835,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Automation|Execution</t>
         </is>
@@ -2845,7 +2860,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Performance|Load</t>
         </is>
@@ -2870,7 +2885,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Performance|Stress</t>
         </is>
@@ -2895,7 +2910,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Performance|Endurance</t>
         </is>
@@ -2903,7 +2918,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2932,7 +2947,7 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3046,7 +3061,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Selenium|Analysis</t>
         </is>
@@ -3094,7 +3109,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Selenium|Design / Scripting</t>
         </is>
@@ -3142,7 +3157,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Selenium|Test Data Prep</t>
         </is>
@@ -3190,7 +3205,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Selenium|Dry Run</t>
         </is>
@@ -3238,7 +3253,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Selenium|Execution</t>
         </is>
@@ -3286,7 +3301,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Playwright|Analysis</t>
         </is>
@@ -3334,7 +3349,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Playwright|Design / Scripting</t>
         </is>
@@ -3382,7 +3397,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Playwright|Test Data Prep</t>
         </is>
@@ -3430,7 +3445,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Playwright|Dry Run</t>
         </is>
@@ -3478,7 +3493,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Playwright|Execution</t>
         </is>
@@ -3526,7 +3541,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Tosca|Analysis</t>
         </is>
@@ -3574,7 +3589,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Tosca|Design / Scripting</t>
         </is>
@@ -3622,7 +3637,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Tosca|Test Data Prep</t>
         </is>
@@ -3670,7 +3685,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Tosca|Dry Run</t>
         </is>
@@ -3718,7 +3733,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Tosca|Execution</t>
         </is>
@@ -3766,7 +3781,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Worksoft|Analysis</t>
         </is>
@@ -3814,7 +3829,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Worksoft|Design / Scripting</t>
         </is>
@@ -3862,7 +3877,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Worksoft|Test Data Prep</t>
         </is>
@@ -3910,7 +3925,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Worksoft|Dry Run</t>
         </is>
@@ -3958,7 +3973,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Worksoft|Execution</t>
         </is>
@@ -3966,7 +3981,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3996,7 +4011,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4120,7 +4135,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Load|LoadRunner|Script Design / Strategy</t>
         </is>
@@ -4173,7 +4188,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Load|LoadRunner|Data Prep</t>
         </is>
@@ -4226,7 +4241,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Load|LoadRunner|Dry Run</t>
         </is>
@@ -4279,7 +4294,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Load|LoadRunner|Analysis</t>
         </is>
@@ -4332,7 +4347,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>Load|LoadRunner|Execution</t>
         </is>
@@ -4385,7 +4400,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Load|NeoLoad|Script Design / Strategy</t>
         </is>
@@ -4438,7 +4453,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Load|NeoLoad|Data Prep</t>
         </is>
@@ -4491,7 +4506,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Load|NeoLoad|Dry Run</t>
         </is>
@@ -4544,7 +4559,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Load|NeoLoad|Analysis</t>
         </is>
@@ -4597,7 +4612,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Load|NeoLoad|Execution</t>
         </is>
@@ -4650,7 +4665,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Stress|LoadRunner|Script Design / Strategy</t>
         </is>
@@ -4703,7 +4718,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Stress|LoadRunner|Data Prep</t>
         </is>
@@ -4756,7 +4771,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Stress|LoadRunner|Dry Run</t>
         </is>
@@ -4809,7 +4824,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Stress|LoadRunner|Analysis</t>
         </is>
@@ -4862,7 +4877,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Stress|LoadRunner|Execution</t>
         </is>
@@ -4915,7 +4930,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Stress|NeoLoad|Script Design / Strategy</t>
         </is>
@@ -4968,7 +4983,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Stress|NeoLoad|Data Prep</t>
         </is>
@@ -5021,7 +5036,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Stress|NeoLoad|Dry Run</t>
         </is>
@@ -5074,7 +5089,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Stress|NeoLoad|Analysis</t>
         </is>
@@ -5127,7 +5142,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Stress|NeoLoad|Execution</t>
         </is>
@@ -5180,7 +5195,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Endurance|LoadRunner|Script Design / Strategy</t>
         </is>
@@ -5233,7 +5248,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Endurance|LoadRunner|Data Prep</t>
         </is>
@@ -5286,7 +5301,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Endurance|LoadRunner|Dry Run</t>
         </is>
@@ -5339,7 +5354,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Endurance|LoadRunner|Analysis</t>
         </is>
@@ -5392,7 +5407,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Endurance|LoadRunner|Execution</t>
         </is>
@@ -5445,7 +5460,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Endurance|NeoLoad|Script Design / Strategy</t>
         </is>
@@ -5498,7 +5513,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>Endurance|NeoLoad|Data Prep</t>
         </is>
@@ -5551,7 +5566,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Endurance|NeoLoad|Dry Run</t>
         </is>
@@ -5604,7 +5619,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Endurance|NeoLoad|Analysis</t>
         </is>
@@ -5657,7 +5672,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>Endurance|NeoLoad|Execution</t>
         </is>
@@ -5665,7 +5680,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -6234,16 +6249,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6261,30 +6275,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Month Weight Pattern</t>
+          <t>Min Team</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Min Team</t>
+          <t>Peak Team</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Peak Team</t>
+          <t>Onshore %</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Onshore %</t>
+          <t>Offshore %</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Offshore %</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Active (Y/N)</t>
         </is>
@@ -6296,24 +6305,19 @@
           <t>Linear</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>1,1,1,1,1,1,1,1,1</t>
-        </is>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="D3" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="E3" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F3" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -6325,24 +6329,19 @@
           <t>Bell Curve</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>0.4,0.7,1.0,1.2,1.2,1.0,0.8,0.5,0.3</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="D4" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="E4" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F4" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -6350,7 +6349,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -6365,109 +6364,467 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>EXPORT SETTINGS</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>STAFFING PROFILE MONTH WEIGHTS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>MonthNumber</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Active (Y/N)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>StaffingProfileWeightKey</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CSVDelimiter</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Staffing plan CSV delimiter</t>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Linear|1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PDFPageSize</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Report export page size</t>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Linear|2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IncludeAssumptions</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Include assumptions in report</t>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Linear|3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ConfigVersion</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>RFP-v1</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Displayed in app</t>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Linear|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Linear|5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Linear|6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Linear|7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Linear|8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Linear|9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Bell Curve|9</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -6676,6 +7033,123 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>EXPORT SETTINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CSVDelimiter</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Staffing plan CSV delimiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PDFPageSize</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Report export page size</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>IncludeAssumptions</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Include assumptions in report</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ConfigVersion</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>RFP-v1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Displayed in app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7247,15 +7721,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7278,7 +7753,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Applicable Sectors</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7294,6 +7769,11 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Active (Y/N)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SAPL1ProcessKey</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7790,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -7324,21 +7804,26 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Energy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>RTR</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Record to Report</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -7352,21 +7837,26 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Utilities</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HTR</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Hire to Retire</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -7380,21 +7870,26 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Oil &amp; Gas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ATR</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Acquire to Retire</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -7408,122 +7903,130 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Tech</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>OTC</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Order to Cash</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Tech;Manufacturing;Life Sciences;Consumer Products</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Replaced by sector-specific OTC variants</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PTM</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Plan to Manufacture</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing;Life Sciences</t>
+          <t>Life Sciences</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Replaced in Retail</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Life Sciences</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Meter-to-Cash</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Meter-to-Cash</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Energy;Utilities</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Replaces OTC</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Retail</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Move-In/Move-Out</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Move-In/Move-Out</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Energy;Utilities</t>
+          <t>Consumer Products</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -7532,26 +8035,31 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Consumer Products</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Device-to-Contract</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Device-to-Contract</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Energy;Utilities</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -7560,26 +8068,31 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Telecom</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Billing Exception Management</t>
+          <t>PTP</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Billing Exception Management</t>
+          <t>Procure to Pay</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Energy;Utilities</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -7588,26 +8101,31 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>PTP|Media</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Credit-to-Collections</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Credit-to-Collections</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Energy;Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -7616,154 +8134,163 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Energy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Hydrocarbon Supply Chain</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Hydrocarbon Supply Chain</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Energy;Oil &amp; Gas</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Replaces OTC/PTP</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Utilities</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Joint Venture Accounting</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Joint Venture Accounting</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Energy;Oil &amp; Gas</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Extends RTR</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Oil &amp; Gas</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Production-to-Revenue</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Production-to-Revenue</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Energy;Oil &amp; Gas</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Extends OTC</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Tech</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Plan-to-Assort</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Plan-to-Assort</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Replaces PTM</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Merchandise-to-Shelf</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Merchandise-to-Shelf</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Life Sciences</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -7772,16 +8299,21 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Life Sciences</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Markdown-to-Margin</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Markdown-to-Margin</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -7791,7 +8323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -7800,234 +8332,1918 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Retail</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Store-to-Customer</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Store-to-Customer</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Consumer Products</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Replaces OTC</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Consumer Products</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Batch-to-Trace</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Batch-to-Trace</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Life Sciences</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Compliance / validation</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Telecom</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Order-to-Activate</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Order-to-Activate</t>
+          <t>Record to Report</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Replaces OTC</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>RTR|Media</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Usage-to-Bill</t>
+          <t>HTR</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Usage-to-Bill</t>
+          <t>Hire to Retire</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Convergent billing</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Energy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Subscribe-to-Renew</t>
+          <t>HTR</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Subscribe-to-Renew</t>
+          <t>Hire to Retire</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Replacement</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Replaces OTC</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Utilities</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Content-to-Cash</t>
+          <t>HTR</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Content-to-Cash</t>
+          <t>Hire to Retire</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Extension</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Rights/ad booking</t>
-        </is>
-      </c>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Oil &amp; Gas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Products</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Consumer Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Hire to Retire</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>HTR|Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Products</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Consumer Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Acquire to Retire</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ATR|Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Order to Cash</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Replaced by sector-specific OTC variants</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>OTC|Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Order to Cash</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Replaced by sector-specific OTC variants</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>OTC|Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Order to Cash</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Replaced by sector-specific OTC variants</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>OTC|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Order to Cash</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Products</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Replaced by sector-specific OTC variants</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>OTC|Consumer Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>PTM</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Plan to Manufacture</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Replaced in Retail</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>PTM|Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>PTM</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Plan to Manufacture</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Replaced in Retail</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>PTM|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Meter-to-Cash|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Move-In/Move-Out|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Device-to-Contract|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Billing Exception Management|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Credit-to-Collections|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC/PTP</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC/PTP</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Hydrocarbon Supply Chain|Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Extends RTR</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Extends RTR</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture Accounting|Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Extends OTC</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue|Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Extends OTC</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Production-to-Revenue|Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Plan-to-Assort</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Plan-to-Assort</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Replaces PTM</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Plan-to-Assort|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Merchandise-to-Shelf</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Merchandise-to-Shelf</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Merchandise-to-Shelf|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Markdown-to-Margin</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Markdown-to-Margin</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Markdown-to-Margin|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Store-to-Customer</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Store-to-Customer</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Store-to-Customer|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Batch-to-Trace</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Batch-to-Trace</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Compliance / validation</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Batch-to-Trace|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Order-to-Activate</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Order-to-Activate</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Order-to-Activate|Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Usage-to-Bill</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Usage-to-Bill</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Convergent billing</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Usage-to-Bill|Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Subscribe-to-Renew</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Subscribe-to-Renew</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Replaces OTC</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Subscribe-to-Renew|Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Content-to-Cash</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Content-to-Cash</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Rights/ad booking</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Content-to-Cash|Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
           <t>Trade-Promotion-to-Settlement</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Trade-Promotion-to-Settlement</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Consumer Products</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Extension</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Extends OTC</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Trade-Promotion-to-Settlement|Consumer Products</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -8338,16 +10554,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8402,7 +10618,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
@@ -8419,16 +10635,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Standard|All</t>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Energy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SAP IS-U</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -8436,114 +10652,393 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>1.15</v>
+      <c r="C4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>SAP IS-U|Utilities</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Utilities</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>IS-Retail</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1.1</v>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>IS-Retail|Retail</t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Oil &amp; Gas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>IS-Oil&amp;Gas</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>1.15</v>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>IS-Oil&amp;Gas|Oil &amp; Gas</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Tech</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Products</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Consumer Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Telecom</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Standard|Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SAP IS-U</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>SAP IS-U|Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IS-Retail</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>IS-Retail|Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>IS-Oil&amp;Gas</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>IS-Oil&amp;Gas|Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>GxP/Validation</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Life Sciences</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C16" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D16" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>GxP/Validation|Life Sciences</t>
         </is>
@@ -8551,7 +11046,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -8574,7 +11069,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8638,7 +11133,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Greenfield|Data Load Validation</t>
         </is>
@@ -8666,7 +11161,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Brownfield|Custom Code Objects for Regression</t>
         </is>
@@ -8694,7 +11189,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Brownfield|Data Conversion Validation</t>
         </is>
@@ -8722,7 +11217,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Bluefield|Custom Code Objects for Regression</t>
         </is>
@@ -8750,7 +11245,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Bluefield|Data Reconciliation Objects</t>
         </is>
@@ -8758,7 +11253,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -8782,7 +11277,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8854,7 +11349,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Pilot Only|Pilot</t>
         </is>
@@ -8885,7 +11380,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Pilot + Rollout|Canada</t>
         </is>
@@ -8916,7 +11411,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Pilot + Rollout|Mexico</t>
         </is>
@@ -8947,7 +11442,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Pilot + Rollout|UK</t>
         </is>
@@ -8955,7 +11450,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Temp2.xlsx
+++ b/Temp2.xlsx
@@ -17,17 +17,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP Implementation" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deployment Reuse" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SFDC Config" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maximo Config" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement Rates" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicability Ratios" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Rates" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Rates" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Rates" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade Rates" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profiles" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profile Weights" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement Rates" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicability Ratios" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Rates" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Rates" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Rates" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade Rates" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profiles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profile Weights" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -274,23 +273,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MaximoConfigTable" displayName="MaximoConfigTable" ref="A2:G8" headerRowCount="1">
-  <autoFilter ref="A2:G8"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Module"/>
-    <tableColumn id="2" name="Process"/>
-    <tableColumn id="3" name="Simple Multiplier"/>
-    <tableColumn id="4" name="Medium Multiplier"/>
-    <tableColumn id="5" name="Complex Multiplier"/>
-    <tableColumn id="6" name="Active (Y/N)"/>
-    <tableColumn id="7" name="MaximoConfigKey"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RequirementComplexityRatesTable" displayName="RequirementComplexityRatesTable" ref="A2:D6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="RequirementComplexityRatesTable" displayName="RequirementComplexityRatesTable" ref="A2:D6" headerRowCount="1">
   <autoFilter ref="A2:D6"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Complexity"/>
@@ -302,8 +285,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E16" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E16" headerRowCount="1">
   <autoFilter ref="A2:E16"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Testing Area"/>
@@ -316,8 +299,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="AutomationLifecycleRatesTable" displayName="AutomationLifecycleRatesTable" ref="A2:L22" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="AutomationLifecycleRatesTable" displayName="AutomationLifecycleRatesTable" ref="A2:L22" headerRowCount="1">
   <autoFilter ref="A2:L22"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Tool"/>
@@ -337,8 +320,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="PerformanceLifecycleRatesTable" displayName="PerformanceLifecycleRatesTable" ref="A2:M32" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="PerformanceLifecycleRatesTable" displayName="PerformanceLifecycleRatesTable" ref="A2:M32" headerRowCount="1">
   <autoFilter ref="A2:M32"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Performance Type"/>
@@ -359,8 +342,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ManualRatesTable" displayName="ManualRatesTable" ref="A2:J8" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="ManualRatesTable" displayName="ManualRatesTable" ref="A2:J8" headerRowCount="1">
   <autoFilter ref="A2:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Sub-Type"/>
@@ -378,8 +361,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="GradeRatesTable" displayName="GradeRatesTable" ref="A2:G8" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="GradeRatesTable" displayName="GradeRatesTable" ref="A2:G8" headerRowCount="1">
   <autoFilter ref="A2:G8"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Grade"/>
@@ -394,8 +377,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:F4" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:F4" headerRowCount="1">
   <autoFilter ref="A2:F4"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Profile"/>
@@ -409,8 +392,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="StaffingProfileWeightsTable" displayName="StaffingProfileWeightsTable" ref="A2:E20" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfileWeightsTable" displayName="StaffingProfileWeightsTable" ref="A2:E20" headerRowCount="1">
   <autoFilter ref="A2:E20"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Profile"/>
@@ -423,9 +406,21 @@
 </table>
 </file>
 
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
+  <autoFilter ref="A2:C6"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Setting"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ApplicationTypesTable" displayName="ApplicationTypesTable" ref="A2:E8" headerRowCount="1">
-  <autoFilter ref="A2:E8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ApplicationTypesTable" displayName="ApplicationTypesTable" ref="A2:E6" headerRowCount="1">
+  <autoFilter ref="A2:E6"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Application Type ID"/>
     <tableColumn id="2" name="Application Type"/>
@@ -438,19 +433,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
-  <autoFilter ref="A2:C6"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Setting"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
   <autoFilter ref="A2:C12"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Assumption ID"/>
@@ -2128,265 +2111,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>MAXIMO MODULE AND PROCESS CONFIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Simple Multiplier</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Medium Multiplier</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Complex Multiplier</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Active (Y/N)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>MaximoConfigKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Work Order Management</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Work Order Planning</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Work Order Management|Work Order Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Asset Management</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Asset Lifecycle</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Asset Management|Asset Lifecycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Preventive Maintenance|Preventive Maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Inventory Management</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Inventory Replenishment</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Inventory Management|Inventory Replenishment</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Procurement Request Flow</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Procurement|Procurement Request Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Service Requests</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Service Request Intake</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Service Requests|Service Request Intake</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2516,7 +2240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2927,7 +2651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3990,7 +3714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5689,7 +5413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5996,7 +5720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6243,7 +5967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6358,7 +6082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6833,206 +6557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>APPLICATION TYPES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Application Type ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Application Type</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Active (Y/N)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Display Order</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Packaged</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>SFDC</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Packaged</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Maximo</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Packaged</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Desktop</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Packaged</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7149,7 +6674,160 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>APPLICATION TYPES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Application Type ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Application Type</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Active (Y/N)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Display Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Packaged</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SFDC</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Packaged</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Temp2.xlsx
+++ b/Temp2.xlsx
@@ -21,12 +21,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicability Ratios" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Rates" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Rates" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Rates" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade Rates" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profiles" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profile Weights" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Rates" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Rates" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade Rates" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profiles" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Profile Weights" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Settings" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumption Templates" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -286,8 +287,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E16" headerRowCount="1">
-  <autoFilter ref="A2:E16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="TestingTypeApplicabilityRatiosTable" displayName="TestingTypeApplicabilityRatiosTable" ref="A2:E20" headerRowCount="1">
+  <autoFilter ref="A2:E20"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Testing Area"/>
     <tableColumn id="2" name="Sub-Type"/>
@@ -343,7 +344,27 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="ManualRatesTable" displayName="ManualRatesTable" ref="A2:J8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="MobileRatesTable" displayName="MobileRatesTable" ref="A2:K6" headerRowCount="1">
+  <autoFilter ref="A2:K6"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="Sub-Type"/>
+    <tableColumn id="2" name="XS"/>
+    <tableColumn id="3" name="S"/>
+    <tableColumn id="4" name="M"/>
+    <tableColumn id="5" name="L"/>
+    <tableColumn id="6" name="XL"/>
+    <tableColumn id="7" name="Default Reuse %"/>
+    <tableColumn id="8" name="Default AI %"/>
+    <tableColumn id="9" name="Default Buffer %"/>
+    <tableColumn id="10" name="Active (Y/N)"/>
+    <tableColumn id="11" name="MobileRateKey"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ManualRatesTable" displayName="ManualRatesTable" ref="A2:J8" headerRowCount="1">
   <autoFilter ref="A2:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Sub-Type"/>
@@ -361,8 +382,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="GradeRatesTable" displayName="GradeRatesTable" ref="A2:G8" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="GradeRatesTable" displayName="GradeRatesTable" ref="A2:G8" headerRowCount="1">
   <autoFilter ref="A2:G8"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Grade"/>
@@ -377,8 +398,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:F4" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfilesTable" displayName="StaffingProfilesTable" ref="A2:F4" headerRowCount="1">
   <autoFilter ref="A2:F4"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Profile"/>
@@ -392,8 +413,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="StaffingProfileWeightsTable" displayName="StaffingProfileWeightsTable" ref="A2:E20" headerRowCount="1">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="StaffingProfileWeightsTable" displayName="StaffingProfileWeightsTable" ref="A2:E20" headerRowCount="1">
   <autoFilter ref="A2:E20"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Profile"/>
@@ -401,18 +422,6 @@
     <tableColumn id="3" name="Weight"/>
     <tableColumn id="4" name="Active (Y/N)"/>
     <tableColumn id="5" name="StaffingProfileWeightKey"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
-  <autoFilter ref="A2:C6"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Setting"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -433,7 +442,19 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ExportSettingsTable" displayName="ExportSettingsTable" ref="A2:C6" headerRowCount="1">
+  <autoFilter ref="A2:C6"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Setting"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="AssumptionTemplatesTable" displayName="AssumptionTemplatesTable" ref="A2:C12" headerRowCount="1">
   <autoFilter ref="A2:C12"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Assumption ID"/>
@@ -2246,11 +2267,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
@@ -2637,6 +2658,106 @@
       <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Performance|Endurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Device Stack</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Mobile|Device Stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Browser Stack</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Mobile|Browser Stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>OS / Version Coverage</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Mobile|OS / Version Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Network / Interrupt</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Mobile|Network / Interrupt</t>
         </is>
       </c>
     </row>
@@ -5419,6 +5540,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>MOBILE TESTING RATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Default Reuse %</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Default AI %</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Default Buffer %</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Active (Y/N)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MobileRateKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Device Stack</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Device Stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Browser Stack</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Browser Stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>OS / Version Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>OS / Version Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Network / Interrupt</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Network / Interrupt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5720,7 +6102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5967,7 +6349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6082,7 +6464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6549,123 +6931,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>EXPORT SETTINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CSVDelimiter</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Staffing plan CSV delimiter</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>PDFPageSize</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Report export page size</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>IncludeAssumptions</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Include assumptions in report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ConfigVersion</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>RFP-v1</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Displayed in app</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -6828,6 +7093,123 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>EXPORT SETTINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CSVDelimiter</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Staffing plan CSV delimiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PDFPageSize</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Report export page size</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>IncludeAssumptions</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Include assumptions in report</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ConfigVersion</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>RFP-v1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Displayed in app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
